--- a/Result/profitability/1326.xlsx
+++ b/Result/profitability/1326.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0625</v>
+        <v>0.23375</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3575</v>
+        <v>4.88625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.74</v>
       </c>
       <c r="M3" t="n">
-        <v>0.32125</v>
+        <v>0.47375</v>
       </c>
       <c r="N3" t="n">
-        <v>5.10125</v>
+        <v>5.44125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6425</v>
+        <v>0.7825</v>
       </c>
       <c r="N4" t="n">
-        <v>5.572500000000001</v>
+        <v>5.88625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-3.96</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1575</v>
+        <v>0.43375</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.65</v>
+        <v>-1.96625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>0.245</v>
+        <v>0.3375</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.95375</v>
+        <v>-2.70625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.45875</v>
+        <v>0.595</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5025</v>
+        <v>-1.21625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.19</v>
       </c>
       <c r="M8" t="n">
-        <v>0.73875</v>
+        <v>0.735</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2675000000000001</v>
+        <v>-0.4425000000000008</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.78625</v>
       </c>
       <c r="N9" t="n">
-        <v>0.13625</v>
+        <v>0.1362499999999995</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.91875</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7762500000000001</v>
+        <v>0.7762499999999997</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>87154</v>
+      </c>
+      <c r="D75" t="n">
+        <v>81627</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5527</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1931</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5115</v>
+      </c>
+      <c r="J75" t="n">
+        <v>7046</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6089</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07500000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.115</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.03000000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.0280373831775701</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1808785529715763</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.888888888888889</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>6.287356321839081</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
